--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N35_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N35_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.2903350787623</v>
+        <v>4.109679450298874</v>
       </c>
       <c r="D2" t="n">
-        <v>11.63249267002355</v>
+        <v>1.890280058878827</v>
       </c>
       <c r="E2" t="n">
-        <v>12.06896408433829</v>
+        <v>1.961206663704972</v>
       </c>
       <c r="F2" t="n">
-        <v>16.17646941552012</v>
+        <v>2.62867628002202</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.64965543462902</v>
+        <v>5.305569008127216</v>
       </c>
       <c r="D3" t="n">
-        <v>32.36241971724706</v>
+        <v>5.258893204052647</v>
       </c>
       <c r="E3" t="n">
-        <v>12.06896408433829</v>
+        <v>1.961206663704972</v>
       </c>
       <c r="F3" t="n">
-        <v>16.17646941552012</v>
+        <v>2.62867628002202</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>6.810505934993397</v>
+        <v>1.106707214436427</v>
       </c>
       <c r="D4" t="n">
-        <v>6.963765545875119</v>
+        <v>1.131611901204707</v>
       </c>
       <c r="E4" t="n">
-        <v>12.06896408433829</v>
+        <v>1.961206663704972</v>
       </c>
       <c r="F4" t="n">
-        <v>16.17646941552012</v>
+        <v>2.62867628002202</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.14803374451859</v>
+        <v>5.54905548348427</v>
       </c>
       <c r="D5" t="n">
-        <v>31.62399659267985</v>
+        <v>5.138899446310476</v>
       </c>
       <c r="E5" t="n">
-        <v>12.06896408433829</v>
+        <v>1.961206663704972</v>
       </c>
       <c r="F5" t="n">
-        <v>16.17646941552012</v>
+        <v>2.62867628002202</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>45.01856271644019</v>
+        <v>7.31551644142153</v>
       </c>
       <c r="D6" t="n">
-        <v>36.18851813823363</v>
+        <v>5.880634197462965</v>
       </c>
       <c r="E6" t="n">
-        <v>12.06896408433829</v>
+        <v>1.961206663704972</v>
       </c>
       <c r="F6" t="n">
-        <v>16.17646941552012</v>
+        <v>2.62867628002202</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>19.51139268336436</v>
+        <v>3.170601311046709</v>
       </c>
       <c r="D7" t="n">
-        <v>55.70232929435327</v>
+        <v>9.051628510332407</v>
       </c>
       <c r="E7" t="n">
-        <v>12.06896408433829</v>
+        <v>1.961206663704972</v>
       </c>
       <c r="F7" t="n">
-        <v>16.17646941552012</v>
+        <v>2.62867628002202</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
